--- a/02_ambientes_limpios_procesos_erp/Caso02_AmbientesLimpios_Procesos_y_ERP.xlsx
+++ b/02_ambientes_limpios_procesos_erp/Caso02_AmbientesLimpios_Procesos_y_ERP.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_Liquidacion_Transportistas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_Conciliacion_Fisico_vs_ERP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_Lee_esto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Liquidacion_Transportistas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Conciliacion_Fisico_vs_ERP" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +53,37 @@
       <color rgb="001E3A8A"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="004B5563"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F2937"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -72,8 +102,18 @@
         <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -109,11 +149,25 @@
         <color rgb="00E5E7EB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F59E0B"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F59E0B"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F59E0B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F59E0B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +183,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,7 +564,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="104" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>DATOS DE EJEMPLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>CASO 02 · AMBIENTES LIMPIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>CONTROL HORARIO, LIQUIDACIÓN DE TRANSPORTE Y CONCILIACIÓN ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Los nombres de transportistas, patentes, fechas, montos y registros de este archivo son ficticios. Se usan solo para mostrar la lógica de control horario, la cuadratura y la conciliación.
+No corresponden a personas, vehículos ni pagos reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Este aviso también aparece en el portafolio web y en el README del caso.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A6:D10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -523,7 +657,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -556,7 +689,6 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -1012,18 +1144,28 @@
         <v/>
       </c>
     </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Datos de ejemplo: nombres, patentes, fechas y montos ficticios. No corresponden a personas, vehículos ni pagos reales.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A19:J19"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1044,7 +1186,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1244,7 +1385,17 @@
         <v/>
       </c>
     </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Datos de ejemplo: nombres, patentes, fechas y montos ficticios. No corresponden a personas, vehículos ni pagos reales.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:I9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>